--- a/artfynd/A 42648-2026 artfynd.xlsx
+++ b/artfynd/A 42648-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153347</v>
       </c>
       <c r="B2" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137153368</v>
       </c>
       <c r="B4" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42648-2026 artfynd.xlsx
+++ b/artfynd/A 42648-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153347</v>
       </c>
       <c r="B2" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137153462</v>
       </c>
       <c r="B3" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137153368</v>
       </c>
       <c r="B4" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137153442</v>
       </c>
       <c r="B5" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137153443</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>137153444</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>137153445</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>137153453</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>137153454</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>137007704</v>
       </c>
       <c r="B11" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>137153393</v>
       </c>
       <c r="B12" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>137153394</v>
       </c>
       <c r="B13" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42648-2026 artfynd.xlsx
+++ b/artfynd/A 42648-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153347</v>
       </c>
       <c r="B2" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137153368</v>
       </c>
       <c r="B4" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42648-2026 artfynd.xlsx
+++ b/artfynd/A 42648-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153347</v>
       </c>
       <c r="B2" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137153462</v>
       </c>
       <c r="B3" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137153368</v>
       </c>
       <c r="B4" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137153442</v>
       </c>
       <c r="B5" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137153443</v>
       </c>
       <c r="B6" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>137153444</v>
       </c>
       <c r="B7" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>137153445</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>137153453</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>137153454</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>137007704</v>
       </c>
       <c r="B11" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>137153393</v>
       </c>
       <c r="B12" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>137153394</v>
       </c>
       <c r="B13" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42648-2026 artfynd.xlsx
+++ b/artfynd/A 42648-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153347</v>
       </c>
       <c r="B2" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137153368</v>
       </c>
       <c r="B4" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42648-2026 artfynd.xlsx
+++ b/artfynd/A 42648-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153347</v>
       </c>
       <c r="B2" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137153462</v>
       </c>
       <c r="B3" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137153368</v>
       </c>
       <c r="B4" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137153442</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137153443</v>
       </c>
       <c r="B6" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>137153444</v>
       </c>
       <c r="B7" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>137153445</v>
       </c>
       <c r="B8" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>137153453</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>137153454</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>137007704</v>
       </c>
       <c r="B11" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>137153393</v>
       </c>
       <c r="B12" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>137153394</v>
       </c>
       <c r="B13" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42648-2026 artfynd.xlsx
+++ b/artfynd/A 42648-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153347</v>
       </c>
       <c r="B2" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137153462</v>
       </c>
       <c r="B3" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137153368</v>
       </c>
       <c r="B4" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137153442</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137153443</v>
       </c>
       <c r="B6" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>137153444</v>
       </c>
       <c r="B7" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>137153445</v>
       </c>
       <c r="B8" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>137153453</v>
       </c>
       <c r="B9" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>137153454</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>137007704</v>
       </c>
       <c r="B11" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>137153393</v>
       </c>
       <c r="B12" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>137153394</v>
       </c>
       <c r="B13" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42648-2026 artfynd.xlsx
+++ b/artfynd/A 42648-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153347</v>
       </c>
       <c r="B2" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137153462</v>
       </c>
       <c r="B3" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137153368</v>
       </c>
       <c r="B4" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137153442</v>
       </c>
       <c r="B5" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137153443</v>
       </c>
       <c r="B6" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>137153444</v>
       </c>
       <c r="B7" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>137153445</v>
       </c>
       <c r="B8" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>137153453</v>
       </c>
       <c r="B9" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>137153454</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>137007704</v>
       </c>
       <c r="B11" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>137153393</v>
       </c>
       <c r="B12" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>137153394</v>
       </c>
       <c r="B13" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42648-2026 artfynd.xlsx
+++ b/artfynd/A 42648-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153347</v>
       </c>
       <c r="B2" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137153462</v>
       </c>
       <c r="B3" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137153368</v>
       </c>
       <c r="B4" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137153442</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137153443</v>
       </c>
       <c r="B6" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>137153444</v>
       </c>
       <c r="B7" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>137153445</v>
       </c>
       <c r="B8" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>137153453</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>137153454</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>137007704</v>
       </c>
       <c r="B11" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>137153393</v>
       </c>
       <c r="B12" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>137153394</v>
       </c>
       <c r="B13" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42648-2026 artfynd.xlsx
+++ b/artfynd/A 42648-2026 artfynd.xlsx
@@ -1772,7 +1772,7 @@
         <v>137007704</v>
       </c>
       <c r="B11" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 42648-2026 artfynd.xlsx
+++ b/artfynd/A 42648-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137153347</v>
       </c>
       <c r="B2" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137153462</v>
       </c>
       <c r="B3" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>137153368</v>
       </c>
       <c r="B4" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>137153442</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>137153443</v>
       </c>
       <c r="B6" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>137153444</v>
       </c>
       <c r="B7" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>137153445</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>137153453</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>137153454</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>137007704</v>
       </c>
       <c r="B11" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>137153393</v>
       </c>
       <c r="B12" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>137153394</v>
       </c>
       <c r="B13" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
